--- a/apps/web/tests/fixtures/coop-registry-synthetic.xlsx
+++ b/apps/web/tests/fixtures/coop-registry-synthetic.xlsx
@@ -40,6 +40,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
 </styleSheet>
 </file>
 

--- a/apps/web/tests/fixtures/coop-registry-synthetic.xlsx
+++ b/apps/web/tests/fixtures/coop-registry-synthetic.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="Rejestr 2025" sheetId="1" r:id="rId1"/>
     <sheet name="Bez nagłówka" sheetId="2" r:id="rId2"/>
+    <sheet name="Bez nr mieszkania" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -521,4 +522,102 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adres</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pow.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cena</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zł/m²</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tytuł własności</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">os. Wymyślone 12</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <v>450000</v>
+      </c>
+      <c r="D2">
+        <v>10000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45671</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spółdzielcze własnościowe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">os. Wymyślone 12</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>450000</v>
+      </c>
+      <c r="D3">
+        <v>8653.85</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">odrębna własność</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4">
+        <v>97</v>
+      </c>
+      <c r="C4">
+        <v>900000</v>
+      </c>
+      <c r="D4">
+        <v>9278.35</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>